--- a/Plan de tests/Informatique/PDTINFO_NOEUD_CAPTEUR.xlsx
+++ b/Plan de tests/Informatique/PDTINFO_NOEUD_CAPTEUR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zevvvf\Documents\Proj Github\CI3-Noeud-de-capteur-\Plan de tests\Informatique\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A89100E-EB0C-4DEC-989D-819373D0DD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7446ABFC-1EA7-4082-8720-45D8FD78FD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CF7E7B00-0B90-4AA1-96DC-F02D56B415EB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
   <si>
     <t>Plan de tests</t>
   </si>
@@ -146,12 +146,6 @@
   </si>
   <si>
     <t>Tout les capteurs s'initialisent et les résultat dans le port série sont correctes.</t>
-  </si>
-  <si>
-    <t>En utilisant le port série. Observer les données des capteurs envoyées par l'ESP32. Le port série devrait ressembler à ceci: SHT_RH: *
-SHT_Temp: *
-luxval: *
-AQI: * (*)      TVOC: * ppb    eCO2: * ppm</t>
   </si>
   <si>
     <t>Soufler sur le board, la valeur eCO2 devrait monter</t>
@@ -209,6 +203,18 @@
   </si>
   <si>
     <t>William Champagne</t>
+  </si>
+  <si>
+    <t>En utilisant le port série. Observer les données des capteurs envoyées par l'ESP32. Le port série devrait ressembler à ceci: SHT_RH: *
+SHT_Temp: *
+luxval: *
+AQI: * (*)      TVOC: * ppb    eCO2: * ppm                                                                  Si la communication ne fonctionne pas, tenter test C1</t>
+  </si>
+  <si>
+    <t>Test conditionnel</t>
+  </si>
+  <si>
+    <t>À l'aide du header I2C sur le PCB, utiliser un analyseur logique pour diagnostiquer une cause potentiel. (Souder le header I2C au besoin)</t>
   </si>
 </sst>
 </file>
@@ -537,55 +543,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -693,6 +650,55 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -821,26 +827,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3E4F9C66-3C4F-4FED-86C7-317DD6AF871B}" name="Table3" displayName="Table3" ref="B10:H20" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15">
-  <autoFilter ref="B10:H20" xr:uid="{3E4F9C66-3C4F-4FED-86C7-317DD6AF871B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3E4F9C66-3C4F-4FED-86C7-317DD6AF871B}" name="Table3" displayName="Table3" ref="B10:H22" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15">
+  <autoFilter ref="B10:H22" xr:uid="{3E4F9C66-3C4F-4FED-86C7-317DD6AF871B}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{21BD1CA3-33DE-44AA-9EB4-FC84914AA01E}" name="Fonction" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{40F1DB91-EE19-4388-9FD9-FC665131A01C}" name="Description du test" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{46119054-E687-474D-A236-70842A202FA2}" name="Résultat" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{E76DCA99-A14D-4F97-96AC-0659630D86A5}" name="Raison réussite ou échec" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{C0DEE3AC-0260-44EA-839D-A616D9FF1BF7}" name="modification effectuée" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{EB8F3DD3-BA06-4471-97FB-7FC066A8F5DD}" name="Nouveau résultat" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{853C2233-5CDD-4625-B476-83FD3F9762B1}" name="Commentaire" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{21BD1CA3-33DE-44AA-9EB4-FC84914AA01E}" name="Fonction" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{40F1DB91-EE19-4388-9FD9-FC665131A01C}" name="Description du test" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{46119054-E687-474D-A236-70842A202FA2}" name="Résultat" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{E76DCA99-A14D-4F97-96AC-0659630D86A5}" name="Raison réussite ou échec" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{C0DEE3AC-0260-44EA-839D-A616D9FF1BF7}" name="modification effectuée" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{EB8F3DD3-BA06-4471-97FB-7FC066A8F5DD}" name="Nouveau résultat" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{853C2233-5CDD-4625-B476-83FD3F9762B1}" name="Commentaire" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6C077BD4-392F-43DD-BBA4-D8EFAD3C2DF3}" name="Table38" displayName="Table38" ref="B2:D15" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" dataCellStyle="Normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6C077BD4-392F-43DD-BBA4-D8EFAD3C2DF3}" name="Table38" displayName="Table38" ref="B2:D15" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" dataCellStyle="Normal">
   <autoFilter ref="B2:D15" xr:uid="{6C077BD4-392F-43DD-BBA4-D8EFAD3C2DF3}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D8886178-DA38-4DAF-A779-65758840ADDA}" name="#" dataDxfId="8" dataCellStyle="Normal">
+    <tableColumn id="1" xr3:uid="{D8886178-DA38-4DAF-A779-65758840ADDA}" name="#" dataDxfId="4" dataCellStyle="Normal">
       <calculatedColumnFormula>B2+1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{F83C734D-9C3E-4041-9C4C-0512ABCBDEB0}" name="Modification suggérée" dataCellStyle="Normal"/>
@@ -1150,7 +1156,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:J38"/>
+  <dimension ref="B1:J40"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -1194,7 +1200,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
@@ -1208,7 +1214,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
@@ -1328,7 +1334,7 @@
         <v>19</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>4</v>
@@ -1351,13 +1357,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>1</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
@@ -1368,13 +1374,13 @@
         <v>11</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>1</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F16" s="18"/>
       <c r="G16" s="18"/>
@@ -1385,13 +1391,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" s="16" t="s">
         <v>1</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
@@ -1402,13 +1408,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D18" s="16" t="s">
         <v>1</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
@@ -1419,19 +1425,19 @@
         <v>19</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D19" s="16" t="s">
         <v>1</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
       <c r="H19" s="18"/>
     </row>
-    <row r="20" spans="2:8" ht="21" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
       <c r="C20" s="15"/>
       <c r="D20" s="16"/>
@@ -1440,26 +1446,38 @@
       <c r="G20" s="18"/>
       <c r="H20" s="18"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="19"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="20"/>
+    <row r="21" spans="2:8" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="1"/>
+      <c r="C21" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="16"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+    </row>
+    <row r="22" spans="2:8" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="16"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="19"/>
-      <c r="C27" s="20"/>
+      <c r="B27" s="20"/>
       <c r="D27" s="20"/>
       <c r="E27" s="20"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="19"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
+      <c r="D28" s="21"/>
       <c r="E28" s="20"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
@@ -1500,11 +1518,15 @@
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="19"/>
+      <c r="C35" s="20"/>
       <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="19"/>
+      <c r="C36" s="20"/>
       <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="19"/>
@@ -1513,18 +1535,26 @@
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="19"/>
       <c r="D38" s="20"/>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B39" s="19"/>
+      <c r="D39" s="20"/>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B40" s="19"/>
+      <c r="D40" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C2:C4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G11:G20 D11:D20">
+  <conditionalFormatting sqref="D11:D22 G11:G22">
     <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Échec">
       <formula>NOT(ISERROR(SEARCH("Échec",D11)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F11:H20">
+  <conditionalFormatting sqref="F11:H22">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$D11=""</formula>
     </cfRule>
@@ -1532,16 +1562,16 @@
       <formula>$D11="Réussi"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G11:G20 D11:D20">
+  <conditionalFormatting sqref="G11:G22 D11:D22">
     <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Réussi">
       <formula>NOT(ISERROR(SEARCH("Réussi",D11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11:B20" xr:uid="{78441C5B-4219-4854-877A-7D3169F5D56F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11:B22" xr:uid="{78441C5B-4219-4854-877A-7D3169F5D56F}">
       <formula1>$J$8:$J$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G20 D11:D20" xr:uid="{FE4B82E2-1996-4D3C-82E2-B8CCB3918355}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G22 D11:D22" xr:uid="{FE4B82E2-1996-4D3C-82E2-B8CCB3918355}">
       <formula1>$J$4:$J$5</formula1>
     </dataValidation>
   </dataValidations>
